--- a/AAII_Financials/Yearly/ONC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ONC_YR_FIN.xlsx
@@ -2573,7 +2573,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>78000</v>
+        <v>134700</v>
       </c>
       <c r="E58" s="3">
         <v>869100</v>
@@ -2615,7 +2615,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>310700</v>
+        <v>254000</v>
       </c>
       <c r="E59" s="3">
         <v>160300</v>
@@ -2699,7 +2699,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1014900</v>
+        <v>1865100</v>
       </c>
       <c r="E61" s="3">
         <v>210800</v>
